--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-3311.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-3311.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -147,27 +147,42 @@
     <t>MCO</t>
   </si>
   <si>
+    <t>Médecine, Chirurgie, Obstétrique</t>
+  </si>
+  <si>
     <t>SSR</t>
   </si>
   <si>
+    <t>Soins de Suite et de Réadaptation</t>
+  </si>
+  <si>
     <t>HD</t>
   </si>
   <si>
     <t>HAD</t>
   </si>
   <si>
+    <t>Hospitalisation À Domicile</t>
+  </si>
+  <si>
     <t>EHPD</t>
   </si>
   <si>
     <t>EHPAD</t>
   </si>
   <si>
+    <t>Établissement d’Hébergement pour Personnes Âgées Dépendantes</t>
+  </si>
+  <si>
     <t>LG_SJR</t>
   </si>
   <si>
     <t>Long séjour</t>
   </si>
   <si>
+    <t>Soins de Longue Durée - long séjour</t>
+  </si>
+  <si>
     <t>MSN_RTRT</t>
   </si>
   <si>
@@ -180,10 +195,16 @@
     <t>Psy</t>
   </si>
   <si>
+    <t>Psychiatrie</t>
+  </si>
+  <si>
     <t>URG</t>
   </si>
   <si>
     <t>Urgence</t>
+  </si>
+  <si>
+    <t>Urgences</t>
   </si>
 </sst>
 </file>
@@ -528,91 +549,107 @@
       <c r="C2" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>63</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-3311.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-3311.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -147,42 +147,27 @@
     <t>MCO</t>
   </si>
   <si>
-    <t>Médecine, Chirurgie, Obstétrique</t>
-  </si>
-  <si>
     <t>SSR</t>
   </si>
   <si>
-    <t>Soins de Suite et de Réadaptation</t>
-  </si>
-  <si>
     <t>HD</t>
   </si>
   <si>
     <t>HAD</t>
   </si>
   <si>
-    <t>Hospitalisation À Domicile</t>
-  </si>
-  <si>
     <t>EHPD</t>
   </si>
   <si>
     <t>EHPAD</t>
   </si>
   <si>
-    <t>Établissement d’Hébergement pour Personnes Âgées Dépendantes</t>
-  </si>
-  <si>
     <t>LG_SJR</t>
   </si>
   <si>
     <t>Long séjour</t>
   </si>
   <si>
-    <t>Soins de Longue Durée - long séjour</t>
-  </si>
-  <si>
     <t>MSN_RTRT</t>
   </si>
   <si>
@@ -195,16 +180,10 @@
     <t>Psy</t>
   </si>
   <si>
-    <t>Psychiatrie</t>
-  </si>
-  <si>
     <t>URG</t>
   </si>
   <si>
     <t>Urgence</t>
-  </si>
-  <si>
-    <t>Urgences</t>
   </si>
 </sst>
 </file>
@@ -549,107 +528,91 @@
       <c r="C2" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="D2" t="s" s="2">
-        <v>44</v>
-      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>49</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>52</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>55</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>57</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>60</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>63</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D9" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-3311.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-3311.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -147,27 +147,42 @@
     <t>MCO</t>
   </si>
   <si>
+    <t>Médecine, Chirurgie, Obstétrique</t>
+  </si>
+  <si>
     <t>SSR</t>
   </si>
   <si>
+    <t>Soins de Suite et de Réadaptation</t>
+  </si>
+  <si>
     <t>HD</t>
   </si>
   <si>
     <t>HAD</t>
   </si>
   <si>
+    <t>Hospitalisation À Domicile</t>
+  </si>
+  <si>
     <t>EHPD</t>
   </si>
   <si>
     <t>EHPAD</t>
   </si>
   <si>
+    <t>Établissement d’Hébergement pour Personnes Âgées Dépendantes</t>
+  </si>
+  <si>
     <t>LG_SJR</t>
   </si>
   <si>
     <t>Long séjour</t>
   </si>
   <si>
+    <t>Soins de Longue Durée - long séjour</t>
+  </si>
+  <si>
     <t>MSN_RTRT</t>
   </si>
   <si>
@@ -180,10 +195,16 @@
     <t>Psy</t>
   </si>
   <si>
+    <t>Psychiatrie</t>
+  </si>
+  <si>
     <t>URG</t>
   </si>
   <si>
     <t>Urgence</t>
+  </si>
+  <si>
+    <t>Urgences</t>
   </si>
 </sst>
 </file>
@@ -528,91 +549,107 @@
       <c r="C2" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>63</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
